--- a/Src/Assets/Common/Tables/Tables/Skill&Buff.xlsx
+++ b/Src/Assets/Common/Tables/Tables/Skill&Buff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F3C27E-AB8D-4F82-A36A-23ACD5BB906D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DBB84D-551E-495C-A1B5-59B48C8D82A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TableExplanation" sheetId="5" r:id="rId1"/>
@@ -3263,7 +3263,7 @@
         <v>506</v>
       </c>
       <c r="C2" s="23" t="str">
-        <f>B2</f>
+        <f t="shared" ref="C2:C10" si="0">B2</f>
         <v>Diving</v>
       </c>
       <c r="D2" s="23" t="s">
@@ -3289,7 +3289,7 @@
         <v>503</v>
       </c>
       <c r="C3" s="21" t="str">
-        <f>B3</f>
+        <f t="shared" si="0"/>
         <v>Stunned</v>
       </c>
       <c r="D3" s="21" t="s">
@@ -3309,7 +3309,7 @@
         <v>500</v>
       </c>
       <c r="C4" s="23" t="str">
-        <f>B4</f>
+        <f t="shared" si="0"/>
         <v>Invincible</v>
       </c>
       <c r="D4" s="23" t="s">
@@ -3337,7 +3337,7 @@
         <v>497</v>
       </c>
       <c r="C5" s="25" t="str">
-        <f>B5</f>
+        <f t="shared" si="0"/>
         <v>Critical</v>
       </c>
       <c r="D5" s="25" t="s">
@@ -3365,7 +3365,7 @@
         <v>494</v>
       </c>
       <c r="C6" s="23" t="str">
-        <f>B6</f>
+        <f t="shared" si="0"/>
         <v>Slowed</v>
       </c>
       <c r="D6" s="23" t="s">
@@ -3393,7 +3393,7 @@
         <v>491</v>
       </c>
       <c r="C7" s="21" t="str">
-        <f>B7</f>
+        <f t="shared" si="0"/>
         <v>Burning</v>
       </c>
       <c r="D7" s="21" t="s">
@@ -3413,7 +3413,7 @@
         <v>488</v>
       </c>
       <c r="C8" s="23" t="str">
-        <f>B8</f>
+        <f t="shared" si="0"/>
         <v>Cocooned</v>
       </c>
       <c r="D8" s="23" t="s">
@@ -3441,7 +3441,7 @@
         <v>485</v>
       </c>
       <c r="C9" s="25" t="str">
-        <f>B9</f>
+        <f t="shared" si="0"/>
         <v>Crystallized</v>
       </c>
       <c r="D9" s="25" t="s">
@@ -3469,7 +3469,7 @@
         <v>482</v>
       </c>
       <c r="C10" s="23" t="str">
-        <f>B10</f>
+        <f t="shared" si="0"/>
         <v>Bleeding</v>
       </c>
       <c r="D10" s="23" t="s">
@@ -3609,7 +3609,7 @@
         <v>478</v>
       </c>
       <c r="B2" s="15" t="str">
-        <f>A2</f>
+        <f t="shared" ref="B2:B26" si="0">A2</f>
         <v>Rapid Supply</v>
       </c>
       <c r="C2" s="15" t="s">
@@ -3648,7 +3648,7 @@
         <v>475</v>
       </c>
       <c r="B3" s="16" t="str">
-        <f>A3</f>
+        <f t="shared" si="0"/>
         <v>Candlelight Sanctuary</v>
       </c>
       <c r="C3" s="16" t="s">
@@ -3691,7 +3691,7 @@
         <v>472</v>
       </c>
       <c r="B4" s="15" t="str">
-        <f>A4</f>
+        <f t="shared" si="0"/>
         <v>Feedback</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -3730,7 +3730,7 @@
         <v>331</v>
       </c>
       <c r="B5" s="16" t="str">
-        <f>A5</f>
+        <f t="shared" si="0"/>
         <v>Critical Strike</v>
       </c>
       <c r="C5" s="16" t="s">
@@ -3773,7 +3773,7 @@
         <v>469</v>
       </c>
       <c r="B6" s="15" t="str">
-        <f>A6</f>
+        <f t="shared" si="0"/>
         <v>Reverse Decision</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -3816,7 +3816,7 @@
         <v>467</v>
       </c>
       <c r="B7" s="16" t="str">
-        <f>A7</f>
+        <f t="shared" si="0"/>
         <v>Bloody Brawl</v>
       </c>
       <c r="C7" s="16" t="s">
@@ -3855,7 +3855,7 @@
         <v>465</v>
       </c>
       <c r="B8" s="15" t="str">
-        <f>A8</f>
+        <f t="shared" si="0"/>
         <v>Battle on All Sides</v>
       </c>
       <c r="C8" s="15" t="s">
@@ -3894,7 +3894,7 @@
         <v>463</v>
       </c>
       <c r="B9" s="16" t="str">
-        <f>A9</f>
+        <f t="shared" si="0"/>
         <v>Short Dagger</v>
       </c>
       <c r="C9" s="16" t="s">
@@ -3933,7 +3933,7 @@
         <v>460</v>
       </c>
       <c r="B10" s="15" t="str">
-        <f>A10</f>
+        <f t="shared" si="0"/>
         <v>Blazing Dance</v>
       </c>
       <c r="C10" s="15" t="s">
@@ -3972,7 +3972,7 @@
         <v>458</v>
       </c>
       <c r="B11" s="16" t="str">
-        <f>A11</f>
+        <f t="shared" si="0"/>
         <v>Poisoned Sword</v>
       </c>
       <c r="C11" s="16" t="s">
@@ -4011,7 +4011,7 @@
         <v>455</v>
       </c>
       <c r="B12" s="15" t="str">
-        <f>A12</f>
+        <f t="shared" si="0"/>
         <v>Mist Shadow Sword</v>
       </c>
       <c r="C12" s="15" t="s">
@@ -4050,7 +4050,7 @@
         <v>451</v>
       </c>
       <c r="B13" s="16" t="str">
-        <f>A13</f>
+        <f t="shared" si="0"/>
         <v>Fight to the Death</v>
       </c>
       <c r="C13" s="16" t="s">
@@ -4089,7 +4089,7 @@
         <v>448</v>
       </c>
       <c r="B14" s="15" t="str">
-        <f>A14</f>
+        <f t="shared" si="0"/>
         <v>Attract Misfortune</v>
       </c>
       <c r="C14" s="15" t="s">
@@ -4132,7 +4132,7 @@
         <v>445</v>
       </c>
       <c r="B15" s="16" t="str">
-        <f>A15</f>
+        <f t="shared" si="0"/>
         <v>Painful Thorns</v>
       </c>
       <c r="C15" s="16" t="s">
@@ -4171,7 +4171,7 @@
         <v>441</v>
       </c>
       <c r="B16" s="15" t="str">
-        <f>A16</f>
+        <f t="shared" si="0"/>
         <v>Crystal Armor</v>
       </c>
       <c r="C16" s="15" t="s">
@@ -4210,7 +4210,7 @@
         <v>438</v>
       </c>
       <c r="B17" s="16" t="str">
-        <f>A17</f>
+        <f t="shared" si="0"/>
         <v>Purification Amulet</v>
       </c>
       <c r="C17" s="16" t="s">
@@ -4249,7 +4249,7 @@
         <v>435</v>
       </c>
       <c r="B18" s="15" t="str">
-        <f>A18</f>
+        <f t="shared" si="0"/>
         <v>Forest's Breath</v>
       </c>
       <c r="C18" s="15" t="s">
@@ -4292,7 +4292,7 @@
         <v>432</v>
       </c>
       <c r="B19" s="16" t="str">
-        <f>A19</f>
+        <f t="shared" si="0"/>
         <v>Cursed Soul's Whisper</v>
       </c>
       <c r="C19" s="16" t="s">
@@ -4335,7 +4335,7 @@
         <v>429</v>
       </c>
       <c r="B20" s="15" t="str">
-        <f>A20</f>
+        <f t="shared" si="0"/>
         <v>Enlighten</v>
       </c>
       <c r="C20" s="15" t="s">
@@ -4374,7 +4374,7 @@
         <v>426</v>
       </c>
       <c r="B21" s="16" t="str">
-        <f>A21</f>
+        <f t="shared" si="0"/>
         <v>Leap Counter</v>
       </c>
       <c r="C21" s="16" t="s">
@@ -4413,7 +4413,7 @@
         <v>423</v>
       </c>
       <c r="B22" s="15" t="str">
-        <f>A22</f>
+        <f t="shared" si="0"/>
         <v>Bloodborne Rebirth</v>
       </c>
       <c r="C22" s="15" t="s">
@@ -4456,7 +4456,7 @@
         <v>420</v>
       </c>
       <c r="B23" s="16" t="str">
-        <f>A23</f>
+        <f t="shared" si="0"/>
         <v>Flawless Defense</v>
       </c>
       <c r="C23" s="16" t="s">
@@ -4499,7 +4499,7 @@
         <v>417</v>
       </c>
       <c r="B24" s="15" t="str">
-        <f>A24</f>
+        <f t="shared" si="0"/>
         <v>Territorial Imprisonment</v>
       </c>
       <c r="C24" s="15" t="s">
@@ -4542,7 +4542,7 @@
         <v>413</v>
       </c>
       <c r="B25" s="16" t="str">
-        <f>A25</f>
+        <f t="shared" si="0"/>
         <v>Immovable as a Bell</v>
       </c>
       <c r="C25" s="16" t="s">
@@ -4581,7 +4581,7 @@
         <v>410</v>
       </c>
       <c r="B26" s="15" t="str">
-        <f>A26</f>
+        <f t="shared" si="0"/>
         <v>Charging Shield</v>
       </c>
       <c r="C26" s="15" t="s">
@@ -5028,7 +5028,7 @@
         <v>393</v>
       </c>
       <c r="C2" s="3" t="str">
-        <f>B2</f>
+        <f t="shared" ref="C2:C33" si="0">B2</f>
         <v>Save Me!!!</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -5081,7 +5081,7 @@
         <v>389</v>
       </c>
       <c r="C3" s="5" t="str">
-        <f>B3</f>
+        <f t="shared" si="0"/>
         <v>Toy Assembly Line</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -5130,7 +5130,7 @@
         <v>385</v>
       </c>
       <c r="C4" s="3" t="str">
-        <f>B4</f>
+        <f t="shared" si="0"/>
         <v>Castle Guardian</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -5183,7 +5183,7 @@
         <v>381</v>
       </c>
       <c r="C5" s="5" t="str">
-        <f>B5</f>
+        <f t="shared" si="0"/>
         <v>Fight Again</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -5236,7 +5236,7 @@
         <v>377</v>
       </c>
       <c r="C6" s="3" t="str">
-        <f>B6</f>
+        <f t="shared" si="0"/>
         <v>Waraxe Dance</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -5287,7 +5287,7 @@
         <v>373</v>
       </c>
       <c r="C7" s="5" t="str">
-        <f>B7</f>
+        <f t="shared" si="0"/>
         <v>Intimidation</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -5338,7 +5338,7 @@
         <v>369</v>
       </c>
       <c r="C8" s="3" t="str">
-        <f>B8</f>
+        <f t="shared" si="0"/>
         <v>Void Servant</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -5389,7 +5389,7 @@
         <v>364</v>
       </c>
       <c r="C9" s="5" t="str">
-        <f>B9</f>
+        <f t="shared" si="0"/>
         <v>Devour the Stars</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -5440,7 +5440,7 @@
         <v>359</v>
       </c>
       <c r="C10" s="3" t="str">
-        <f>B10</f>
+        <f t="shared" si="0"/>
         <v>Morphing Remains</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -5491,7 +5491,7 @@
         <v>355</v>
       </c>
       <c r="C11" s="5" t="str">
-        <f>B11</f>
+        <f t="shared" si="0"/>
         <v>Charge</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -5544,7 +5544,7 @@
         <v>351</v>
       </c>
       <c r="C12" s="3" t="str">
-        <f>B12</f>
+        <f t="shared" si="0"/>
         <v>Time Reversal</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -5597,7 +5597,7 @@
         <v>347</v>
       </c>
       <c r="C13" s="5" t="str">
-        <f>B13</f>
+        <f t="shared" si="0"/>
         <v>Cocooning</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -5650,7 +5650,7 @@
         <v>343</v>
       </c>
       <c r="C14" s="3" t="str">
-        <f>B14</f>
+        <f t="shared" si="0"/>
         <v>Strengthen with Battle</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -5701,7 +5701,7 @@
         <v>339</v>
       </c>
       <c r="C15" s="5" t="str">
-        <f>B15</f>
+        <f t="shared" si="0"/>
         <v>Dark Embrace</v>
       </c>
       <c r="D15" s="5" t="s">
@@ -5754,7 +5754,7 @@
         <v>335</v>
       </c>
       <c r="C16" s="3" t="str">
-        <f>B16</f>
+        <f t="shared" si="0"/>
         <v>Enlightenment on High Fort</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -5805,7 +5805,7 @@
         <v>331</v>
       </c>
       <c r="C17" s="5" t="str">
-        <f>B17</f>
+        <f t="shared" si="0"/>
         <v>Critical Strike</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -5856,7 +5856,7 @@
         <v>327</v>
       </c>
       <c r="C18" s="3" t="str">
-        <f>B18</f>
+        <f t="shared" si="0"/>
         <v>Adjudication</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -5907,7 +5907,7 @@
         <v>323</v>
       </c>
       <c r="C19" s="5" t="str">
-        <f>B19</f>
+        <f t="shared" si="0"/>
         <v>Judgment</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -5958,7 +5958,7 @@
         <v>319</v>
       </c>
       <c r="C20" s="3" t="str">
-        <f>B20</f>
+        <f t="shared" si="0"/>
         <v>Prismatic Essence</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -6009,7 +6009,7 @@
         <v>315</v>
       </c>
       <c r="C21" s="5" t="str">
-        <f>B21</f>
+        <f t="shared" si="0"/>
         <v>Tactical Turtle</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -6060,7 +6060,7 @@
         <v>311</v>
       </c>
       <c r="C22" s="3" t="str">
-        <f>B22</f>
+        <f t="shared" si="0"/>
         <v>Blazing Armor</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -6111,7 +6111,7 @@
         <v>307</v>
       </c>
       <c r="C23" s="5" t="str">
-        <f>B23</f>
+        <f t="shared" si="0"/>
         <v>Beat Down</v>
       </c>
       <c r="D23" s="5" t="s">
@@ -6164,7 +6164,7 @@
         <v>302</v>
       </c>
       <c r="C24" s="3" t="str">
-        <f>B24</f>
+        <f t="shared" si="0"/>
         <v>Simulacrum</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -6217,7 +6217,7 @@
         <v>298</v>
       </c>
       <c r="C25" s="5" t="str">
-        <f>B25</f>
+        <f t="shared" si="0"/>
         <v>Loot in Chaos</v>
       </c>
       <c r="D25" s="5" t="s">
@@ -6268,7 +6268,7 @@
         <v>294</v>
       </c>
       <c r="C26" s="3" t="str">
-        <f>B26</f>
+        <f t="shared" si="0"/>
         <v>Blessing</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -6321,7 +6321,7 @@
         <v>290</v>
       </c>
       <c r="C27" s="5" t="str">
-        <f>B27</f>
+        <f t="shared" si="0"/>
         <v>Divine Retribution</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -6374,7 +6374,7 @@
         <v>285</v>
       </c>
       <c r="C28" s="3" t="str">
-        <f>B28</f>
+        <f t="shared" si="0"/>
         <v>Dual Genesis</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -6425,7 +6425,7 @@
         <v>281</v>
       </c>
       <c r="C29" s="5" t="str">
-        <f>B29</f>
+        <f t="shared" si="0"/>
         <v>Fluid Dance Morphology</v>
       </c>
       <c r="D29" s="5" t="s">
@@ -6476,7 +6476,7 @@
         <v>277</v>
       </c>
       <c r="C30" s="3" t="str">
-        <f>B30</f>
+        <f t="shared" si="0"/>
         <v>Mirror Shred</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -6527,7 +6527,7 @@
         <v>273</v>
       </c>
       <c r="C31" s="5" t="str">
-        <f>B31</f>
+        <f t="shared" si="0"/>
         <v>Ethereal Emergence</v>
       </c>
       <c r="D31" s="5" t="s">
@@ -6578,7 +6578,7 @@
         <v>269</v>
       </c>
       <c r="C32" s="3" t="str">
-        <f>B32</f>
+        <f t="shared" si="0"/>
         <v>Crystal Bloom</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -6629,7 +6629,7 @@
         <v>265</v>
       </c>
       <c r="C33" s="5" t="str">
-        <f>B33</f>
+        <f t="shared" si="0"/>
         <v>Final Curtain</v>
       </c>
       <c r="D33" s="5" t="s">
@@ -6680,7 +6680,7 @@
         <v>261</v>
       </c>
       <c r="C34" s="3" t="str">
-        <f>B34</f>
+        <f t="shared" ref="C34:C65" si="1">B34</f>
         <v>Water Warding Incantation</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -6731,7 +6731,7 @@
         <v>256</v>
       </c>
       <c r="C35" s="5" t="str">
-        <f>B35</f>
+        <f t="shared" si="1"/>
         <v>Supply Line</v>
       </c>
       <c r="D35" s="5" t="s">
@@ -6782,7 +6782,7 @@
         <v>252</v>
       </c>
       <c r="C36" s="3" t="str">
-        <f>B36</f>
+        <f t="shared" si="1"/>
         <v>88mm Tank Gun</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -6833,7 +6833,7 @@
         <v>248</v>
       </c>
       <c r="C37" s="5" t="str">
-        <f>B37</f>
+        <f t="shared" si="1"/>
         <v>Body of Steel</v>
       </c>
       <c r="D37" s="5" t="s">
@@ -6884,7 +6884,7 @@
         <v>244</v>
       </c>
       <c r="C38" s="3" t="str">
-        <f>B38</f>
+        <f t="shared" si="1"/>
         <v>Will-o'-the-Wisp Rekindled</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -6935,7 +6935,7 @@
         <v>240</v>
       </c>
       <c r="C39" s="5" t="str">
-        <f>B39</f>
+        <f t="shared" si="1"/>
         <v>800mm Railgun</v>
       </c>
       <c r="D39" s="5" t="s">
@@ -6986,7 +6986,7 @@
         <v>236</v>
       </c>
       <c r="C40" s="3" t="str">
-        <f>B40</f>
+        <f t="shared" si="1"/>
         <v>Assemble</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -7037,7 +7037,7 @@
         <v>232</v>
       </c>
       <c r="C41" s="5" t="str">
-        <f>B41</f>
+        <f t="shared" si="1"/>
         <v>Load Shells</v>
       </c>
       <c r="D41" s="5" t="s">
@@ -7088,7 +7088,7 @@
         <v>228</v>
       </c>
       <c r="C42" s="3" t="str">
-        <f>B42</f>
+        <f t="shared" si="1"/>
         <v>White Specter's Tear</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -7139,7 +7139,7 @@
         <v>224</v>
       </c>
       <c r="C43" s="5" t="str">
-        <f>B43</f>
+        <f t="shared" si="1"/>
         <v>Shared Origin_Pale</v>
       </c>
       <c r="D43" s="5" t="s">
@@ -7190,7 +7190,7 @@
         <v>222</v>
       </c>
       <c r="C44" s="3" t="str">
-        <f>B44</f>
+        <f t="shared" si="1"/>
         <v>Black Specter's Wing</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -7241,7 +7241,7 @@
         <v>217</v>
       </c>
       <c r="C45" s="5" t="str">
-        <f>B45</f>
+        <f t="shared" si="1"/>
         <v>Shared Origin_Abyss</v>
       </c>
       <c r="D45" s="5" t="s">
@@ -7292,7 +7292,7 @@
         <v>213</v>
       </c>
       <c r="C46" s="3" t="str">
-        <f>B46</f>
+        <f t="shared" si="1"/>
         <v>Animism</v>
       </c>
       <c r="D46" s="3" t="s">
@@ -7345,7 +7345,7 @@
         <v>208</v>
       </c>
       <c r="C47" s="5" t="str">
-        <f>B47</f>
+        <f t="shared" si="1"/>
         <v>Run Wild and Crash</v>
       </c>
       <c r="D47" s="5" t="s">
@@ -7396,7 +7396,7 @@
         <v>204</v>
       </c>
       <c r="C48" s="3" t="str">
-        <f>B48</f>
+        <f t="shared" si="1"/>
         <v>Entangle</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -7447,7 +7447,7 @@
         <v>199</v>
       </c>
       <c r="C49" s="5" t="str">
-        <f>B49</f>
+        <f t="shared" si="1"/>
         <v>Pouncing Strike</v>
       </c>
       <c r="D49" s="5" t="s">
@@ -7498,7 +7498,7 @@
         <v>195</v>
       </c>
       <c r="C50" s="3" t="str">
-        <f>B50</f>
+        <f t="shared" si="1"/>
         <v>Left Hand</v>
       </c>
       <c r="D50" s="3" t="s">
@@ -7547,7 +7547,7 @@
         <v>192</v>
       </c>
       <c r="C51" s="5" t="str">
-        <f>B51</f>
+        <f t="shared" si="1"/>
         <v>Right Hand</v>
       </c>
       <c r="D51" s="5" t="s">
@@ -7596,7 +7596,7 @@
         <v>189</v>
       </c>
       <c r="C52" s="3" t="str">
-        <f>B52</f>
+        <f t="shared" si="1"/>
         <v>Linked Hearts</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -7647,7 +7647,7 @@
         <v>185</v>
       </c>
       <c r="C53" s="5" t="str">
-        <f>B53</f>
+        <f t="shared" si="1"/>
         <v>Fear No More!</v>
       </c>
       <c r="D53" s="5" t="s">
@@ -7698,7 +7698,7 @@
         <v>181</v>
       </c>
       <c r="C54" s="3" t="str">
-        <f>B54</f>
+        <f t="shared" si="1"/>
         <v>Wavebreaker</v>
       </c>
       <c r="D54" s="3" t="s">
